--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566597726</v>
+        <v>46157.93093471987</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93093471987</v>
+        <v>46157.93170115892</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93170115892</v>
+        <v>46157.93398446501</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398446501</v>
+        <v>46157.93716184076</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716184076</v>
+        <v>46158.28214785227</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214785227</v>
+        <v>46158.29676260117</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676260117</v>
+        <v>46158.29812899372</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812899372</v>
+        <v>46158.33385784204</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385784204</v>
+        <v>46158.36855532329</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/8. ООО АЛЕКО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855532329</v>
+        <v>46158.3728627003</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
